--- a/mapping_sap_procosa_full.xlsx
+++ b/mapping_sap_procosa_full.xlsx
@@ -578,18 +578,22 @@
           <t>The candidate 'Tax Situation Code for CBS and IBS' closely matches the semantic role of 'Tipo de Imposto CBS' and has a high name confidence.</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>0.8696</v>
       </c>
       <c r="Q2" t="n">
         <v>0.8696</v>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>no_mapping_exists</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>c96 is the 3-digit CST ('000'/'410'), claimed by m176 - a situation code, not a tax type. No column in this export holds a 4-char SAP tax type (full scan: 1 hit, c11 'PR05', already accepted to m29). Model m1 is 0/209.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -617,7 +621,6 @@
       <c r="G3" t="n">
         <v>0.1888</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>0.98</v>
       </c>
@@ -636,14 +639,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -692,18 +687,12 @@
           <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0.98</v>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -731,7 +720,6 @@
       <c r="G5" t="n">
         <v>0.1521</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>0.98</v>
       </c>
@@ -750,14 +738,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -785,7 +765,6 @@
       <c r="G6" t="n">
         <v>0.1173</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>0.9055</v>
       </c>
@@ -804,14 +783,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -839,7 +810,6 @@
       <c r="G7" t="n">
         <v>0.1124</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>0.9209000000000001</v>
       </c>
@@ -858,14 +828,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -876,8 +838,6 @@
           <t>Base Reduzida CBS</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>0.8776</v>
       </c>
@@ -908,18 +868,12 @@
           <t>All candidates exhibit semantic-role conflicts with the target column, indicating incompatible meanings.</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -968,18 +922,22 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>no_mapping_exists</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>c117 is a SAP X/blank boolean ('X' in 15296 rows, 1 distinct). Writing 'X' beside ICM3/IPI3/ICON/IPSN would fabricate a tax type.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1007,7 +965,6 @@
       <c r="G10" t="n">
         <v>0.2118</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
         <v>0.9866</v>
       </c>
@@ -1026,14 +983,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1061,7 +1010,6 @@
       <c r="G11" t="n">
         <v>0.1095</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>0.98</v>
       </c>
@@ -1080,14 +1028,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1115,7 +1055,6 @@
       <c r="G12" t="n">
         <v>0.1049</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>0.98</v>
       </c>
@@ -1134,14 +1073,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1190,18 +1121,22 @@
           <t>The candidate 'IBSM Excl. Base' has a matching numeric type and no semantic header conflict, despite all values being zero.</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0.8986</v>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>CAVEAT: delivers an all-zero column (18209 filled, 1 distinct, 0 non-zero). Same precedent as m19. Originally withheld by 0.0014 of confidence.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1229,7 +1164,6 @@
       <c r="G14" t="n">
         <v>0.1288</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>0.9231</v>
       </c>
@@ -1248,14 +1182,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1266,8 +1192,6 @@
           <t>Base Reduzida IBSM</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>0.8987000000000001</v>
       </c>
@@ -1298,18 +1222,12 @@
           <t>All candidates exhibit semantic header conflicts and lack distinctive row evidence.</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1358,18 +1276,22 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>no_mapping_exists</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>c95 is a 3-char SAP tax-LAW code {RJ3:10929, RA0:5915, RH5:25} and a perfect 1:1 recode of the already-accepted c97, carrying zero independent information. The model has no 'Lei CBS/IBS' column.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1397,7 +1319,6 @@
       <c r="G17" t="n">
         <v>0.1869</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>0.98</v>
       </c>
@@ -1416,14 +1337,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1472,18 +1385,12 @@
           <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0.98</v>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1511,7 +1418,6 @@
       <c r="G19" t="n">
         <v>0.0864</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>0.98</v>
       </c>
@@ -1530,14 +1436,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1586,18 +1484,22 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>CAVEAT: delivers an all-zero column (18209 filled, 1 distinct, 0 non-zero). Legitimate fiscal data - precedent set by the already-accepted all-zero c101-&gt;m5 Isentas CBS. Populated, never empty.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1646,18 +1548,22 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Confirmed: third member of a set already accepted twice (c102-&gt;m6, c116-&gt;m13). Profiles near-identical: non-zero 9344/9400/9425, distinct 3285/3337/3355. Accepting two and withholding the third was arbitrary.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1668,8 +1574,6 @@
           <t>Base Reduzida IBS</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>0.8747</v>
       </c>
@@ -1700,18 +1604,12 @@
           <t>All candidates exhibit semantic header conflicts and lack distinctive sample evidence.</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1760,18 +1658,22 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>no_mapping_exists</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>c110 is a SAP X/blank boolean, 1 distinct. No Imposto Seletivo block exists: regex seletiv|excise|imp.sel over all 118 headers returns ZERO hits, and c98-c118 is a strict 3x7 grid (CBS/IBSS/IBSM) with no fourth block.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1820,18 +1722,22 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>no_mapping_exists</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>c61 is Base FCP (Fundo de Combate a Pobreza), an ICMS surcharge - a different tax. 1 distinct, 0 non-zero. Correct home is m112. Procosa levies no IS.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1880,18 +1786,22 @@
           <t>The header 'Alíquota FCP' closely matches the role of 'Aliquota IS' and has a higher name confidence.</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>0.8259</v>
       </c>
       <c r="Q25" t="n">
         <v>0.8259</v>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>no_mapping_exists</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>c62 is Aliquota FCP, same group; 1 distinct, 0 non-zero. Correct home is m113. Procosa levies no IS.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1940,18 +1850,22 @@
           <t>The candidate 'Valor do imposto' has a strong name match and similar numeric profile, despite both being all zeros.</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
         <v>0.8486</v>
       </c>
       <c r="Q26" t="n">
         <v>0.8486</v>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>no_mapping_exists</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>c77 'Valor do imposto' is a generic unqualified label, 1 distinct, 0 non-zero. Shipping it would assert an Imposto Seletivo of exactly zero on 18209 invoices - a positive claim the data does not support.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2000,18 +1914,22 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>no_mapping_exists</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>c115 is the IBSM period's exempt-base slot and belongs to m12. Procosa levies no IS.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2060,18 +1978,22 @@
           <t>The name 'ICMS Outro mont.básico' aligns with the tax context of 'Outras IS', and the numeric profile supports potential mapping despite some zero values.</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
         <v>0.8376</v>
       </c>
       <c r="Q28" t="n">
         <v>0.8376</v>
       </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>no_mapping_exists</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>c60 is real ICMS money (7953 non-zero rows, R$66,303,765.04) and belongs to m45 by the book identity. Would misattribute R$66.3M of ICMS to a tax the client does not levy.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2082,8 +2004,6 @@
           <t>Base Reduzida IS</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>0.8255</v>
       </c>
@@ -2114,18 +2034,12 @@
           <t>All candidates exhibit semantic-role conflicts with the target column, indicating incompatible meanings.</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2153,7 +2067,6 @@
       <c r="G30" t="n">
         <v>0.1805</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>1</v>
       </c>
@@ -2172,14 +2085,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2228,18 +2133,22 @@
           <t>The header 'NF Data lançamento' closely matches 'Data de lançamento' and both have strong datetime evidence.</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
         <v>0.9</v>
       </c>
       <c r="Q31" t="n">
         <v>0.9</v>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Confirmed: c4 is 12 distinct over a 14-day window, the posting-period signature. Swap with c3 refuted quantitatively.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2288,18 +2197,22 @@
           <t>The candidate 'SAP Nº do NF' has a strong name match and a similar numeric format with a fixed digit width of 7, aligning well with the 'Nº de documento'.</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
         <v>0.9</v>
       </c>
       <c r="Q32" t="n">
         <v>0.9</v>
       </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Confirmed: chave decomposition proves m31 is not the NF number (m32==key[25:34] in 209/209 model rows, m31 in 0/209). c1 is 18209/18209 filled, 2823 distinct, 100% 7-digit, matching model m31 shape.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2348,18 +2261,12 @@
           <t>The candidate 'Nº NF-e' has a high name confidence and closely matches the numeric structure and length of 'Nº da Nota Fiscal'.</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
         <v>0.95</v>
       </c>
       <c r="Q33" t="n">
         <v>0.93</v>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2387,7 +2294,6 @@
       <c r="G34" t="n">
         <v>0.1677</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
         <v>0.98</v>
       </c>
@@ -2406,14 +2312,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2441,7 +2339,6 @@
       <c r="G35" t="n">
         <v>0.0654</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
         <v>1</v>
       </c>
@@ -2471,11 +2368,6 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2524,18 +2416,12 @@
           <t>The candidate 'CFOP descrição' has a strong name match and sufficient distinctive sample overlap with the 'Descrição' column.</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
         <v>0.4443</v>
       </c>
       <c r="Q36" t="n">
         <v>0.8588</v>
       </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2584,18 +2470,22 @@
           <t>The candidate 'NF ID parceir' has a high name confidence and similar numeric structure, but lacks distinctive sample overlap with the ID parceiro.</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
         <v>0.5</v>
       </c>
       <c r="Q37" t="n">
         <v>0.75</v>
       </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>CAVEAT: 604 of 18209 rows (3.32%) hold 6-digit IDs and ~3090 hold alphanumeric partner codes ('BAP283G','COS826'), against model m36's 7-digit numeric exemplars. Swap with c6 arithmetically impossible (c5 83% pure-numeric; c6 0% numeric).</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2606,8 +2496,6 @@
           <t>Nome</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>0.8272</v>
       </c>
@@ -2638,18 +2526,25 @@
           <t>No candidate column matches the semantic role of 'Nome' as they all pertain to different data types or contexts.</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>incorrect</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>6</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Confirmed: only party-name column in the export, 18209/18209 filled, 258 distinct, matching c5's 267 partner IDs; shares the SAP NAME1 35-char truncation with model m37.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2660,8 +2555,6 @@
           <t>Nº ID fiscal 1</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
         <v>0.8163</v>
       </c>
@@ -2692,18 +2585,25 @@
           <t>The semantic header conflict and lack of distinctive sample overlap indicate that 'Nº NF-e' does not match the 'Nº ID fiscal 1'.</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>incorrect</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>32</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Only tax-ID column in the export and only fiscal-ID column in the model. 18154/18192 (99.79%) pass the CNPJ check digit. *** CAVEAT: MUST NOT SHIP UNNORMALISED. All values are punctuated ('71.960.736/0001-50'); model m38 is 209/209 bare digits. apply_invoice_mapping.py copies verbatim with no normalisation hook. Strip non-digits before delivery or any join. 38 rows never resolve (foreign/placeholder); 17 blank. ***</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2714,8 +2614,6 @@
           <t>Região</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
         <v>0.7377</v>
       </c>
@@ -2746,18 +2644,12 @@
           <t>No suitable candidate matches the semantic role of 'Região' based on header names and data evidence.</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2806,18 +2698,12 @@
           <t>The candidate 'NF Valor lí' has a high name confidence and a similar numeric profile, but the median values differ significantly.</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
         <v>0.8</v>
       </c>
       <c r="Q41" t="n">
         <v>0.85</v>
       </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2866,18 +2752,12 @@
           <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
         <v>0.9983</v>
       </c>
       <c r="Q42" t="n">
         <v>0.9063</v>
       </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2905,7 +2785,6 @@
       <c r="G43" t="n">
         <v>0.0654</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>0.9832</v>
       </c>
@@ -2924,14 +2803,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2942,8 +2813,6 @@
           <t>Valor ICMS_ST</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
         <v>0.8414</v>
       </c>
@@ -2974,18 +2843,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
         <v>0.8414</v>
       </c>
       <c r="Q44" t="n">
         <v>0.8414</v>
       </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3034,18 +2897,22 @@
           <t>The candidate 'ICMS Mont.base excl.' has a strong name match and a similar numeric profile, despite a higher zero fraction.</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
         <v>0.9</v>
       </c>
       <c r="Q45" t="n">
         <v>0.85</v>
       </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Confirmed: book identity c8 Total == c12 + c59 + c60 holds on 17022/18209 (93.5%) vs 51.3% / 50.5% / 8.4% for the alternatives. Direction fixed by accepted precedents c68-&gt;m51, c70-&gt;m124, c101-&gt;m5. NOTE: carries R$46.4M (54.3%) of base-reduction excess rather than true exemption.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3094,18 +2961,22 @@
           <t>The candidate 'ICMS Outro mont.básico' has a high name confidence and a similar numeric profile, despite some differences in sample values.</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
         <v>0.9429999999999999</v>
       </c>
       <c r="Q46" t="n">
         <v>0.921</v>
       </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Confirmed: the firm's own de_para for this client has Outras ICMS ~= Outras IPI (equal rowwise 96/99). Only this pairing reproduces it: c60==c68 on 12263/18209 with 7881 both non-zero; the swapped pairing has 6. NOTE: also explains the 319 delivered rows with ICMS value&gt;0 against a zero base.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3154,18 +3025,12 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3176,8 +3041,6 @@
           <t>Valor ICEP</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
         <v>0.8563</v>
       </c>
@@ -3208,18 +3071,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0.8563</v>
       </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3268,18 +3125,12 @@
           <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
         <v>0.9986</v>
       </c>
       <c r="Q49" t="n">
         <v>0.9142</v>
       </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3307,7 +3158,6 @@
       <c r="G50" t="n">
         <v>0.0513</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>0.982</v>
       </c>
@@ -3326,14 +3176,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3382,18 +3224,22 @@
           <t>The candidate 'IPI Mont.base excl.' aligns with the 'Isentas IPI' column in terms of numeric type and lacks semantic conflicts.</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
         <v>0.7623</v>
       </c>
       <c r="Q51" t="n">
         <v>0.8629</v>
       </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>CAVEAT: near-vacuous - 18209 filled but only 6 NON-ZERO rows (7 distinct), R$199,626.89 across 6 export lines. Not empty, so not a fabrication, but of very low value. Shipped for family completeness with ICMS/IPI/CBS/IBS/IBSM.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3421,7 +3267,6 @@
       <c r="G52" t="n">
         <v>0.0999</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>0.9133</v>
       </c>
@@ -3440,14 +3285,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3496,18 +3333,12 @@
           <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
         <v>0.9994</v>
       </c>
       <c r="Q53" t="n">
         <v>0.8959</v>
       </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3535,7 +3366,6 @@
       <c r="G54" t="n">
         <v>0.1132</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>0.9897</v>
       </c>
@@ -3554,14 +3384,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3610,18 +3432,12 @@
           <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
         <v>0.9994</v>
       </c>
       <c r="Q55" t="n">
         <v>0.9123</v>
       </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3649,7 +3465,6 @@
       <c r="G56" t="n">
         <v>0.1032</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>0.9866</v>
       </c>
@@ -3668,14 +3483,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3686,8 +3493,6 @@
           <t>Frete</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
         <v>0.7621</v>
       </c>
@@ -3718,18 +3523,12 @@
           <t>All candidates have weak evidence and do not semantically align with 'Frete'.</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
         <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0.7621</v>
       </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3740,8 +3539,6 @@
           <t>Seguros</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
         <v>0.8034</v>
       </c>
@@ -3772,18 +3569,12 @@
           <t>The candidate columns contain non-informative data with all zeros, making them incompatible with the 'Seguros' column.</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
         <v>0.8034</v>
       </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3811,7 +3602,6 @@
       <c r="G59" t="n">
         <v>0.1786</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>0.9808</v>
       </c>
@@ -3830,14 +3620,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3848,8 +3630,6 @@
           <t>Chave de acesso</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
         <v>0.7518</v>
       </c>
@@ -3880,18 +3660,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
         <v>0.7518</v>
       </c>
       <c r="Q60" t="n">
         <v>0.7518</v>
       </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3919,7 +3693,6 @@
       <c r="G61" t="n">
         <v>0.08939999999999999</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>0.9337</v>
       </c>
@@ -3938,14 +3711,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3994,18 +3759,22 @@
           <t>The column 'NF Data documento' has a high name confidence and matches the datetime format of the canonical 'Data documento'.</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
         <v>0.9</v>
       </c>
       <c r="Q62" t="n">
         <v>0.9</v>
       </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Confirmed: model invariant m61&lt;=m30 holds 209/209; client reproduces it exactly, c3&lt;=c4 in 18209/18209. Swap would fail in 9702 rows (53.28%).</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4016,8 +3785,6 @@
           <t>Criado por</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
         <v>0.8194</v>
       </c>
@@ -4048,18 +3815,12 @@
           <t>No candidate column matches the semantic role of 'Criado por'.</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4070,8 +3831,6 @@
           <t>Modificado por</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
         <v>0.7532</v>
       </c>
@@ -4102,18 +3861,12 @@
           <t>No candidate column matches the semantic role of 'Modificado por'.</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4124,8 +3877,6 @@
           <t>Criado Manualmente</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
         <v>0.7963</v>
       </c>
@@ -4156,18 +3907,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
         <v>0.7963</v>
       </c>
       <c r="Q65" t="n">
         <v>0.7963</v>
       </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4216,18 +3961,12 @@
           <t>The header 'SAP Nº do NF' closely matches the semantic role of 'Nº doc.original Cabeçalho' and has a strong numeric profile.</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
         <v>0.8283</v>
       </c>
       <c r="Q66" t="n">
         <v>0.8283</v>
       </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4276,18 +4015,12 @@
           <t>The candidate 'Nº NF-e' closely matches the original document number with high numeric similarity and a strong name match.</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
         <v>0.9</v>
       </c>
       <c r="Q67" t="n">
         <v>0.85</v>
       </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4336,18 +4069,12 @@
           <t>The candidate's name suggests a tax situation code, but the numeric profile and all-zero evidence do not support a valid mapping.</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
         <v>0.5</v>
       </c>
       <c r="Q68" t="n">
         <v>0.8231000000000001</v>
       </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4396,18 +4123,12 @@
           <t>The candidate 'Nº NF-e' has a strong name match and informative data profile, indicating it likely represents the invoice number.</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
       <c r="P69" t="n">
         <v>0.8423</v>
       </c>
       <c r="Q69" t="n">
         <v>0.8423</v>
       </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4418,8 +4139,6 @@
           <t>Condições pagamento</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
         <v>0.7769</v>
       </c>
@@ -4450,18 +4169,12 @@
           <t>No suitable candidate matches the semantic role of 'Condições pagamento'.</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4472,8 +4185,6 @@
           <t>Base ICAP</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
         <v>0.7418</v>
       </c>
@@ -4504,18 +4215,12 @@
           <t>All candidates exhibit strong semantic header conflicts with the 'Base ICAP' role, indicating they do not represent the same business meaning.</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4526,8 +4231,6 @@
           <t>Aliquota ICAP</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
         <v>0.7465000000000001</v>
       </c>
@@ -4558,18 +4261,12 @@
           <t>All candidates exhibit strong semantic header conflicts with the target column, indicating incompatible tax roles.</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
         <v>0</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4580,8 +4277,6 @@
           <t>NºID fiscal regional</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
         <v>0.8206</v>
       </c>
@@ -4612,18 +4307,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
         <v>0.6917</v>
       </c>
       <c r="Q73" t="n">
         <v>0.805</v>
       </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4672,18 +4361,12 @@
           <t>The candidate 'NF item' has a high name confidence and a numeric profile that aligns well with the expected format for invoice items.</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
       <c r="P74" t="n">
         <v>0.9</v>
       </c>
       <c r="Q74" t="n">
         <v>0.9</v>
       </c>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4694,8 +4377,6 @@
           <t>Mensagem</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
         <v>0.7887</v>
       </c>
@@ -4726,18 +4407,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
       <c r="P75" t="n">
         <v>0.7887</v>
       </c>
       <c r="Q75" t="n">
         <v>0.7887</v>
       </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4748,8 +4423,6 @@
           <t>Setor industrial</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
         <v>0.7939000000000001</v>
       </c>
@@ -4780,18 +4453,12 @@
           <t>The candidate columns contain no relevant data to support a mapping to 'Setor industrial'.</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
         <v>0</v>
       </c>
       <c r="Q76" t="n">
         <v>0.7939000000000001</v>
       </c>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4802,8 +4469,6 @@
           <t>Domicílio fiscal</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
         <v>0.7764</v>
       </c>
@@ -4834,18 +4499,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
       <c r="P77" t="n">
         <v>0.9</v>
       </c>
       <c r="Q77" t="n">
         <v>0.85</v>
       </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4856,8 +4515,6 @@
           <t>Modelo nota fiscal</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
         <v>0.8329</v>
       </c>
@@ -4888,18 +4545,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
       <c r="P78" t="n">
         <v>0.5</v>
       </c>
       <c r="Q78" t="n">
         <v>0.5</v>
       </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4948,18 +4599,12 @@
           <t>The candidate 'Nº NF-e' has a high name confidence and a substantial number of non-empty values, indicating it likely represents the invoice number.</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
         <v>0.8714</v>
       </c>
       <c r="Q79" t="n">
         <v>0.8714</v>
       </c>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5008,18 +4653,12 @@
           <t>The candidate 'Texto breve de material' has a high name confidence and a substantial non-empty count, indicating it likely represents a description of services.</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
       <c r="P80" t="n">
         <v>0.742</v>
       </c>
       <c r="Q80" t="n">
         <v>0.8935</v>
       </c>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5030,8 +4669,6 @@
           <t>Origem do material</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
         <v>0.8397</v>
       </c>
@@ -5062,18 +4699,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
       <c r="P81" t="n">
         <v>0.8</v>
       </c>
       <c r="Q81" t="n">
         <v>0.85</v>
       </c>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5122,18 +4753,12 @@
           <t>The candidate 'Utilização do' has a high name confidence and a numeric profile that aligns closely with the expected binary values.</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
         <v>0.995</v>
       </c>
       <c r="Q82" t="n">
         <v>0.8925</v>
       </c>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5144,8 +4769,6 @@
           <t>Tipo de avaliação</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
         <v>0.8351</v>
       </c>
@@ -5176,18 +4799,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
         <v>0.8</v>
       </c>
       <c r="Q83" t="n">
         <v>0.8351</v>
       </c>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5215,7 +4832,6 @@
       <c r="G84" t="n">
         <v>0.1256</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
         <v>1</v>
       </c>
@@ -5234,14 +4850,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5269,7 +4877,6 @@
       <c r="G85" t="n">
         <v>0.2098</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
         <v>1</v>
       </c>
@@ -5288,14 +4895,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5306,8 +4905,6 @@
           <t>Grupo de imposto</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
         <v>0.7895</v>
       </c>
@@ -5338,18 +4935,12 @@
           <t>All candidates exhibit semantic-role conflicts with the 'Grupo de imposto' header, indicating incompatible mappings.</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5360,8 +4951,6 @@
           <t>Tipo de Imposto ICMS</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
         <v>0.8341</v>
       </c>
@@ -5392,18 +4981,12 @@
           <t>All candidates exhibit semantic-role conflicts with the target column, indicating incompatible mappings.</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
       <c r="P87" t="n">
         <v>0</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5414,8 +4997,6 @@
           <t>Base Reduzida ICMS</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
         <v>0.8585</v>
       </c>
@@ -5446,18 +5027,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
         <v>0.8585</v>
       </c>
       <c r="Q88" t="n">
         <v>0.8585</v>
       </c>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5468,8 +5043,6 @@
           <t>Tipo de Imposto ICAP</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
         <v>0.8243</v>
       </c>
@@ -5500,18 +5073,12 @@
           <t>No suitable candidate matches the semantic role of 'Tipo de Imposto ICAP'.</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5522,8 +5089,6 @@
           <t>Isentas ICAP</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
         <v>0.8137</v>
       </c>
@@ -5554,18 +5119,12 @@
           <t>All candidates exhibit tax-family conflicts with the target column, and no strong evidence supports a mapping.</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
         <v>0</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5576,8 +5135,6 @@
           <t>Outras ICAP</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
         <v>0.8452</v>
       </c>
@@ -5608,18 +5165,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
         <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5630,8 +5181,6 @@
           <t>Base Reduzida ICAP</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
         <v>0.8386</v>
       </c>
@@ -5662,18 +5211,12 @@
           <t>All candidates exhibit tax-family conflicts and contain only zeros, providing no valid mapping evidence.</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
       <c r="P92" t="n">
         <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5684,8 +5227,6 @@
           <t>Tipo de Imposto ICEP</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
         <v>0.8214</v>
       </c>
@@ -5716,18 +5257,12 @@
           <t>No viable candidates due to semantic conflicts and lack of relevant data evidence.</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
       <c r="P93" t="n">
         <v>0</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5738,8 +5273,6 @@
           <t>Base ICEP</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
         <v>0.8491</v>
       </c>
@@ -5770,18 +5303,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
       <c r="P94" t="n">
         <v>0</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5792,8 +5319,6 @@
           <t>Aliquota ICEP</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
         <v>0.8585</v>
       </c>
@@ -5824,18 +5349,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
       <c r="P95" t="n">
         <v>0</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5846,8 +5365,6 @@
           <t>Isentas ICEP</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
         <v>0.8115</v>
       </c>
@@ -5878,18 +5395,12 @@
           <t>All candidates exhibit tax-family conflicts with the ICEP column, indicating incompatible semantic roles.</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
       <c r="P96" t="n">
         <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5900,8 +5411,6 @@
           <t>Outras ICEP</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
         <v>0.805</v>
       </c>
@@ -5932,18 +5441,12 @@
           <t>All candidates exhibit tax-family conflicts with ICEP, indicating they do not semantically align with the intended mapping.</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
         <v>0</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5954,8 +5457,6 @@
           <t>Base Reduzida ICEP</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
         <v>0.8177</v>
       </c>
@@ -5986,18 +5487,12 @@
           <t>All candidates have semantic header conflicts with the ICEP tax family, indicating incompatible mappings.</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
       <c r="P98" t="n">
         <v>0</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6008,8 +5503,6 @@
           <t>Tipo de Imposto ICSP</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
         <v>0.8250999999999999</v>
       </c>
@@ -6040,18 +5533,12 @@
           <t>All candidates exhibit semantic-role conflicts or lack relevant data evidence.</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
       <c r="P99" t="n">
         <v>0</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6062,8 +5549,6 @@
           <t>Base ICSP</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
         <v>0.8551</v>
       </c>
@@ -6094,18 +5579,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
       <c r="P100" t="n">
         <v>0</v>
       </c>
       <c r="Q100" t="n">
         <v>0.8551</v>
       </c>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6116,8 +5595,6 @@
           <t>Aliquota ICSP</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
         <v>0.873</v>
       </c>
@@ -6148,18 +5625,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
       <c r="P101" t="n">
         <v>0</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6208,18 +5679,12 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
       <c r="P102" t="n">
         <v>0</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6230,8 +5695,6 @@
           <t>Isentas ICSP</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
         <v>0.8142</v>
       </c>
@@ -6262,18 +5725,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
         <v>0.8142</v>
       </c>
       <c r="Q103" t="n">
         <v>0.8142</v>
       </c>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6284,8 +5741,6 @@
           <t>Outras ICSP</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="n">
         <v>0.8473000000000001</v>
       </c>
@@ -6316,18 +5771,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
       <c r="P104" t="n">
         <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6338,8 +5787,6 @@
           <t>Base Reduzida ICSP</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
         <v>0.8278</v>
       </c>
@@ -6370,18 +5817,12 @@
           <t>All candidates have semantic header conflicts with the original column, indicating incompatible tax-family roles.</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
         <v>0</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6392,8 +5833,6 @@
           <t>Tipo de Imposto DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
         <v>0.8171</v>
       </c>
@@ -6424,18 +5863,12 @@
           <t>All candidates exhibit semantic-role conflicts and lack sufficient evidence to support a mapping.</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
       </c>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6446,8 +5879,6 @@
           <t>Base DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
         <v>0.8024</v>
       </c>
@@ -6478,18 +5909,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
       <c r="P107" t="n">
         <v>0.8024</v>
       </c>
       <c r="Q107" t="n">
         <v>0.8024</v>
       </c>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6538,18 +5963,12 @@
           <t>The header 'Alíquota FCP' closely matches the expected role of a tax rate, aligning with the 'Aliquota DIF_ALIQ' despite both having all-zero values.</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
       <c r="P108" t="n">
         <v>0.827</v>
       </c>
       <c r="Q108" t="n">
         <v>0.827</v>
       </c>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6560,8 +5979,6 @@
           <t>Valor DIF_ALIQ</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="n">
         <v>0.8483000000000001</v>
       </c>
@@ -6592,18 +6009,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
       <c r="P109" t="n">
         <v>0</v>
       </c>
       <c r="Q109" t="n">
         <v>0.8483000000000001</v>
       </c>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6652,18 +6063,12 @@
           <t>The candidate 'Alíq. TOT. ICMS + FCP' has a strong name match but both columns contain only zeros, indicating no valid data evidence.</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>0.834</v>
       </c>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6712,18 +6117,12 @@
           <t>The candidate 'Alíq. TOT. ICMS + FCP' has a strong name match but both columns contain only zeros, indicating no valid data evidence.</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
       <c r="P111" t="n">
         <v>0</v>
       </c>
       <c r="Q111" t="n">
         <v>0.8368</v>
       </c>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6772,18 +6171,12 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6832,18 +6225,12 @@
           <t>The name 'Base FCP' closely aligns with 'Base ICMS_FECP', despite both having all-zero evidence.</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
         <v>0.8895999999999999</v>
       </c>
       <c r="Q113" t="n">
         <v>0.8895999999999999</v>
       </c>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6892,18 +6279,12 @@
           <t>The candidate 'Alíquota FCP' has a high name confidence and matches the semantic role of a tax rate, despite all values being zero.</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="n">
         <v>0.9056</v>
       </c>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6952,18 +6333,12 @@
           <t>The candidate 'Valor tot. ICMS + FCP' has a high name confidence and matches the semantic role of a tax value despite both columns having all zero values.</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
       <c r="P115" t="n">
         <v>0.9292</v>
       </c>
       <c r="Q115" t="n">
         <v>0.9292</v>
       </c>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7012,18 +6387,12 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
       <c r="P116" t="n">
         <v>0</v>
       </c>
       <c r="Q116" t="n">
         <v>0.8229</v>
       </c>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7072,18 +6441,12 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
       <c r="P117" t="n">
         <v>0</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7094,8 +6457,6 @@
           <t>Base Reduzida ICMS_FECP</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
         <v>0.8636</v>
       </c>
@@ -7126,18 +6487,12 @@
           <t>All candidates exhibit semantic-role conflicts and lack distinctive non-zero evidence.</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
         <v>0</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
-      <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7148,8 +6503,6 @@
           <t>Base Reduzida IPI</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="n">
         <v>0.8697</v>
       </c>
@@ -7180,18 +6533,12 @@
           <t>All candidates exhibit semantic-role conflicts with the target column, and no distinctive row evidence supports a mapping.</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7202,8 +6549,6 @@
           <t>Tipo de Imposto COFINS</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="n">
         <v>0.8409</v>
       </c>
@@ -7234,18 +6579,12 @@
           <t>All candidates exhibit semantic-role conflicts and lack relevant data evidence.</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
       <c r="P120" t="n">
         <v>0</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7294,18 +6633,12 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
         <v>0</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7354,18 +6687,22 @@
           <t>The candidate 'COFINS Outro mont.básico' has a high name confidence and aligns with the semantic role of 'Outras COFINS', despite some numeric discrepancies.</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
       <c r="P122" t="n">
         <v>0.8946</v>
       </c>
       <c r="Q122" t="n">
         <v>0.8946</v>
       </c>
-      <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Confirmed: exact structural twin of the already-accepted c70-&gt;m124 Outras PIS (5266 vs 5265 distinct, 12277 vs 12276 non-zero).</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7376,8 +6713,6 @@
           <t>Base Reduzida COFINS</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
         <v>0.8582</v>
       </c>
@@ -7408,18 +6743,12 @@
           <t>All candidates exhibit semantic header conflicts and lack distinctive non-zero evidence.</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
       <c r="P123" t="n">
         <v>0</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
-      <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
-      <c r="T123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7468,18 +6797,12 @@
           <t>The candidate 'PIS Mont.base excl.' has a strong name match and no semantic conflicts, despite both columns having all-zero evidence.</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
       <c r="P124" t="n">
         <v>0.8593</v>
       </c>
       <c r="Q124" t="n">
         <v>0.8593</v>
       </c>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7507,7 +6830,6 @@
       <c r="G125" t="n">
         <v>0.125</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="n">
         <v>0.9081</v>
       </c>
@@ -7526,14 +6848,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7544,8 +6858,6 @@
           <t>Tipo de Imposto PIS</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="n">
         <v>0.8179</v>
       </c>
@@ -7576,18 +6888,12 @@
           <t>All candidates exhibit semantic-role conflicts or lack relevant evidence to support a mapping.</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
       <c r="P126" t="n">
         <v>0</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
       </c>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
-      <c r="T126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7598,8 +6904,6 @@
           <t>Base Reduzida PIS</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="n">
         <v>0.8646</v>
       </c>
@@ -7630,18 +6934,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
       <c r="P127" t="n">
         <v>0</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
-      <c r="T127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7652,8 +6950,6 @@
           <t>Tipo de Imposto ISS</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="n">
         <v>0.8248</v>
       </c>
@@ -7684,18 +6980,12 @@
           <t>All candidates exhibit semantic header conflicts or lack relevant data evidence.</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
       <c r="P128" t="n">
         <v>0</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
-      <c r="T128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7706,8 +6996,6 @@
           <t>Base ISS</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
         <v>0.8614000000000001</v>
       </c>
@@ -7738,18 +7026,12 @@
           <t>All candidates have a semantic header conflict with the expected tax family, and their evidence is insufficient to support a mapping.</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
       <c r="P129" t="n">
         <v>0</v>
       </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7760,8 +7042,6 @@
           <t>Aliquota ISS</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="n">
         <v>0.8131</v>
       </c>
@@ -7792,18 +7072,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
       <c r="P130" t="n">
         <v>0.8131</v>
       </c>
       <c r="Q130" t="n">
         <v>0.8131</v>
       </c>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7852,18 +7126,12 @@
           <t>The candidate 'Valor do imposto' has a high name confidence but lacks distinctive sample evidence.</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
       <c r="P131" t="n">
         <v>0</v>
       </c>
       <c r="Q131" t="n">
         <v>0.8705000000000001</v>
       </c>
-      <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7874,8 +7142,6 @@
           <t>Isentas ISS</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="n">
         <v>0.8234</v>
       </c>
@@ -7906,18 +7172,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
       <c r="P132" t="n">
         <v>0.8234</v>
       </c>
       <c r="Q132" t="n">
         <v>0.8234</v>
       </c>
-      <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7928,8 +7188,6 @@
           <t>Outras ISS</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
         <v>0.8365</v>
       </c>
@@ -7960,18 +7218,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
         <v>0</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
-      <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7982,8 +7234,6 @@
           <t>Base Reduzida ISS</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="n">
         <v>0.8275</v>
       </c>
@@ -8014,18 +7264,12 @@
           <t>All candidates have semantic header conflicts with the tax-family context, indicating they do not match the intended role of 'Base Reduzida ISS'.</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
       <c r="P134" t="n">
         <v>0</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8036,8 +7280,6 @@
           <t>Base FECP_ST</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="n">
         <v>0.9218</v>
       </c>
@@ -8068,18 +7310,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
       <c r="P135" t="n">
         <v>0</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
-      <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8090,8 +7326,6 @@
           <t>Aliquota FECP_ST</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
         <v>0.9108000000000001</v>
       </c>
@@ -8122,18 +7356,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
       <c r="P136" t="n">
         <v>0</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
-      <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8144,8 +7372,6 @@
           <t>Valor FECP_ST</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
         <v>0.9346</v>
       </c>
@@ -8176,18 +7402,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
       <c r="P137" t="n">
         <v>0</v>
       </c>
       <c r="Q137" t="n">
         <v>0.9346</v>
       </c>
-      <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
-      <c r="T137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8198,8 +7418,6 @@
           <t>Isentas FECP_ST</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="n">
         <v>0.8204</v>
       </c>
@@ -8230,18 +7448,12 @@
           <t>All candidates have significant semantic header conflicts and lack distinctive row evidence.</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
       <c r="P138" t="n">
         <v>0</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8252,8 +7464,6 @@
           <t>Outras FECP_ST</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="n">
         <v>0.8443000000000001</v>
       </c>
@@ -8284,18 +7494,12 @@
           <t>All candidates have semantic header conflicts and provide no distinctive row evidence.</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
       <c r="P139" t="n">
         <v>0</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
-      <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8306,8 +7510,6 @@
           <t>Base Reduzida FECP_ST</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
         <v>0.8651</v>
       </c>
@@ -8338,18 +7540,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
-      <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
-      <c r="T140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8360,8 +7556,6 @@
           <t>Tipo de Imposto ICMS_ST</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
         <v>0.8159</v>
       </c>
@@ -8392,18 +7586,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
       <c r="P141" t="n">
         <v>0.7407</v>
       </c>
       <c r="Q141" t="n">
         <v>0.8159</v>
       </c>
-      <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8414,8 +7602,6 @@
           <t>Base ICMS_ST</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="n">
         <v>0.8875</v>
       </c>
@@ -8446,18 +7632,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
       <c r="P142" t="n">
         <v>0.5</v>
       </c>
       <c r="Q142" t="n">
         <v>0.8875</v>
       </c>
-      <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8468,8 +7648,6 @@
           <t>Aliquota ICMS_ST</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
         <v>0.8486</v>
       </c>
@@ -8500,18 +7678,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
       <c r="P143" t="n">
         <v>0.8486</v>
       </c>
       <c r="Q143" t="n">
         <v>0.8486</v>
       </c>
-      <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
-      <c r="T143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8522,8 +7694,6 @@
           <t>Isentas ICMS_ST</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="n">
         <v>0.8415</v>
       </c>
@@ -8554,18 +7724,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
       <c r="P144" t="n">
         <v>0</v>
       </c>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
-      <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8576,8 +7740,6 @@
           <t>Outras ICMS_ST</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
         <v>0.8381999999999999</v>
       </c>
@@ -8608,18 +7770,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
       <c r="P145" t="n">
         <v>0</v>
       </c>
       <c r="Q145" t="n">
         <v>0.8381999999999999</v>
       </c>
-      <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
-      <c r="T145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8630,8 +7786,6 @@
           <t>Base Reduzida ICMS_ST</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
         <v>0.8447</v>
       </c>
@@ -8662,18 +7816,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
       <c r="P146" t="n">
         <v>0.5</v>
       </c>
       <c r="Q146" t="n">
         <v>0.5</v>
       </c>
-      <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
-      <c r="T146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8684,8 +7832,6 @@
           <t>Ctg.class.cont.</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
         <v>0.8198</v>
       </c>
@@ -8716,18 +7862,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
       <c r="P147" t="n">
         <v>0.8198</v>
       </c>
       <c r="Q147" t="n">
         <v>0.8198</v>
       </c>
-      <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8738,8 +7878,6 @@
           <t>Municipio Inicio</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="n">
         <v>0.7607</v>
       </c>
@@ -8770,18 +7908,12 @@
           <t>All candidate columns lack relevant data evidence and do not match the expected semantic role.</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
       <c r="P148" t="n">
         <v>0</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
       </c>
-      <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
-      <c r="T148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8830,18 +7962,22 @@
           <t>The header 'NF Data de criação' closely matches 'Data de criação' and both contain datetime values.</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
       <c r="P149" t="n">
         <v>0.9421</v>
       </c>
       <c r="Q149" t="n">
         <v>0.9421</v>
       </c>
-      <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
-      <c r="T149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Confirmed: residual of the proven date trio; c4&lt;=c26 in 18179/18209 (99.84%), mirroring model m30==m148 in 208/209.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8852,8 +7988,6 @@
           <t>Criado às:</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="n">
         <v>0.7014</v>
       </c>
@@ -8884,18 +8018,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
       <c r="P150" t="n">
         <v>0.7364000000000001</v>
       </c>
       <c r="Q150" t="n">
         <v>0.7364000000000001</v>
       </c>
-      <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -8906,8 +8034,6 @@
           <t>Exercício</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="n">
         <v>0.8296</v>
       </c>
@@ -8938,18 +8064,12 @@
           <t>No viable candidate due to lack of non-empty values in the 'Exercício' column.</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
       <c r="P151" t="n">
         <v>0</v>
       </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
-      <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8960,8 +8080,6 @@
           <t>Redução</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="n">
         <v>0.8004</v>
       </c>
@@ -8992,18 +8110,12 @@
           <t>All candidates have weak evidence with all-zero values, indicating no valid mapping.</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
       <c r="P152" t="n">
         <v>0</v>
       </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
-      <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -9014,8 +8126,6 @@
           <t>Data de estorno</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="n">
         <v>0.7699</v>
       </c>
@@ -9046,18 +8156,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
       <c r="P153" t="n">
         <v>0.7699</v>
       </c>
       <c r="Q153" t="n">
         <v>0.7699</v>
       </c>
-      <c r="R153" t="inlineStr"/>
-      <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -9068,8 +8172,6 @@
           <t>Cód.domicílio fiscal</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
         <v>0.8129</v>
       </c>
@@ -9100,18 +8202,12 @@
           <t>All candidate columns have empty or insufficient evidence, making a mapping unsupported.</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
       <c r="P154" t="n">
         <v>0</v>
       </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
-      <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -9122,8 +8218,6 @@
           <t>Domicílio Fiscal</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
         <v>0.8124</v>
       </c>
@@ -9154,18 +8248,12 @@
           <t>No suitable candidate found due to lack of evidence in the client data.</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
       <c r="P155" t="n">
         <v>0</v>
       </c>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
-      <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
-      <c r="T155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -9176,8 +8264,6 @@
           <t>Dt. Faturamento Ent.</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="n">
         <v>0.822</v>
       </c>
@@ -9208,18 +8294,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
       <c r="P156" t="n">
         <v>0.822</v>
       </c>
       <c r="Q156" t="n">
         <v>0.822</v>
       </c>
-      <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
-      <c r="T156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -9230,8 +8310,6 @@
           <t>ID do consumidor final</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
         <v>0.7791</v>
       </c>
@@ -9262,18 +8340,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
       <c r="P157" t="n">
         <v>0.7791</v>
       </c>
       <c r="Q157" t="n">
         <v>0.7791</v>
       </c>
-      <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
-      <c r="T157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -9284,8 +8356,6 @@
           <t>Dest.</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
         <v>0.7147</v>
       </c>
@@ -9316,18 +8386,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
       <c r="P158" t="n">
         <v>0.7147</v>
       </c>
       <c r="Q158" t="n">
         <v>0.7147</v>
       </c>
-      <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
-      <c r="T158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -9376,18 +8440,12 @@
           <t>The candidate 'Nº NF-e' has high name confidence and a strong numeric profile, closely matching the expected format for NF-e numbers.</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
       <c r="P159" t="n">
         <v>0.9</v>
       </c>
       <c r="Q159" t="n">
         <v>0.9367</v>
       </c>
-      <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
-      <c r="T159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -9398,8 +8456,6 @@
           <t>Código verificação</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
         <v>0.846</v>
       </c>
@@ -9430,18 +8486,12 @@
           <t>The client column 'Código verificação' has no non-empty values, making it impossible to establish a mapping.</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
       <c r="P160" t="n">
         <v>0</v>
       </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
-      <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
-      <c r="T160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9452,8 +8502,6 @@
           <t>Ordem</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
         <v>0.8094</v>
       </c>
@@ -9484,18 +8532,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
       <c r="P161" t="n">
         <v>0.8094</v>
       </c>
       <c r="Q161" t="n">
         <v>0.8094</v>
       </c>
-      <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
-      <c r="T161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -9544,18 +8586,12 @@
           <t>The name 'Despesas líquidas' closely matches 'Despesas', and while both have high zero fractions, the name confidence supports a mapping.</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
       <c r="P162" t="n">
         <v>0.8894</v>
       </c>
       <c r="Q162" t="n">
         <v>0.8894</v>
       </c>
-      <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
-      <c r="T162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -9566,8 +8602,6 @@
           <t>Centro custo</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="n">
         <v>0.7773</v>
       </c>
@@ -9598,18 +8632,12 @@
           <t>The candidate columns contain no relevant data to support a mapping to 'Centro custo'.</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
       <c r="P163" t="n">
         <v>0</v>
       </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
-      <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
-      <c r="T163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -9620,8 +8648,6 @@
           <t>Municipio Fim</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="n">
         <v>0.7657</v>
       </c>
@@ -9652,18 +8678,12 @@
           <t>All client candidates have weak evidence and do not align semantically with 'Municipio Fim'.</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
       <c r="P164" t="n">
         <v>0</v>
       </c>
       <c r="Q164" t="n">
         <v>0.7574</v>
       </c>
-      <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
-      <c r="T164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -9674,8 +8694,6 @@
           <t>Nº material antigo</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
         <v>0.841</v>
       </c>
@@ -9706,18 +8724,12 @@
           <t>No viable candidate exists due to the empty evidence quality of the model column.</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
       <c r="P165" t="n">
         <v>0</v>
       </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
-      <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
-      <c r="T165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -9766,18 +8778,12 @@
           <t>The header 'Item do pedido' has a high name confidence and matches the expected item code role despite weak data evidence.</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
       <c r="P166" t="n">
         <v>0.8828</v>
       </c>
       <c r="Q166" t="n">
         <v>0.8828</v>
       </c>
-      <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
-      <c r="T166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -9826,18 +8832,12 @@
           <t>The column 'Nº NF-e' has a high name confidence and contains valid numeric samples consistent with the expected format for NFC-e numbers.</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
       <c r="P167" t="n">
         <v>0.9</v>
       </c>
       <c r="Q167" t="n">
         <v>0.8863</v>
       </c>
-      <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
-      <c r="T167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -9848,8 +8848,6 @@
           <t>CódCtaAnalítica cont.D/C</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
         <v>0.7791</v>
       </c>
@@ -9880,18 +8878,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
       <c r="P168" t="n">
         <v>0.3188</v>
       </c>
       <c r="Q168" t="n">
         <v>0.7791</v>
       </c>
-      <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
-      <c r="T168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -9902,8 +8894,6 @@
           <t>Valor da isenção de ICMS</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="n">
         <v>0.8313</v>
       </c>
@@ -9934,18 +8924,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
       <c r="P169" t="n">
         <v>0.8313</v>
       </c>
       <c r="Q169" t="n">
         <v>0.8313</v>
       </c>
-      <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -9994,18 +8978,12 @@
           <t>The name 'Base FCP' closely aligns with 'Base de Cálculo ICOP FECP', despite both having all-zero evidence.</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
       <c r="P170" t="n">
         <v>0.8962</v>
       </c>
       <c r="Q170" t="n">
         <v>0.8962</v>
       </c>
-      <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
-      <c r="T170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -10054,18 +9032,12 @@
           <t>The candidate 'Alíquota FCP' has a high name confidence and matches the semantic role of a tax rate, despite both columns having all-zero evidence.</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
       <c r="P171" t="n">
         <v>0</v>
       </c>
       <c r="Q171" t="n">
         <v>0.9145</v>
       </c>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
-      <c r="T171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -10114,18 +9086,12 @@
           <t>The candidate 'Valor FCP' has a high name confidence and matches the semantic role, despite all values being zero.</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
       <c r="P172" t="n">
         <v>0</v>
       </c>
       <c r="Q172" t="n">
         <v>0.9141</v>
       </c>
-      <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
-      <c r="T172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -10136,8 +9102,6 @@
           <t>Isentas ICOP FECP</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr"/>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="n">
         <v>0.8399</v>
       </c>
@@ -10168,18 +9132,12 @@
           <t>All candidates exhibit semantic-role conflicts with the exempt status of the original column.</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
       <c r="P173" t="n">
         <v>0</v>
       </c>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
-      <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
-      <c r="T173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -10190,8 +9148,6 @@
           <t>Outras ICOP FECP</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
         <v>0.8458</v>
       </c>
@@ -10222,18 +9178,12 @@
           <t>All candidates exhibit semantic-role conflicts and lack distinctive evidence.</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
       <c r="P174" t="n">
         <v>0</v>
       </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
-      <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
-      <c r="T174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -10261,7 +9211,6 @@
       <c r="G175" t="n">
         <v>0.0883</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
         <v>0.98</v>
       </c>
@@ -10280,14 +9229,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
-      <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr"/>
-      <c r="T175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -10298,8 +9239,6 @@
           <t>Centro de lucro</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="n">
         <v>0.7947</v>
       </c>
@@ -10330,18 +9269,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
       <c r="P176" t="n">
         <v>0.7947</v>
       </c>
       <c r="Q176" t="n">
         <v>0.7947</v>
       </c>
-      <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
-      <c r="T176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -10407,9 +9340,16 @@
       <c r="Q177" t="n">
         <v>0.901</v>
       </c>
-      <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
-      <c r="T177" t="inlineStr"/>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Confirmed structurally: c96==c97[:3] in 16869/16869 rows (100%), and c97-&gt;m177 is already accepted. Catalog ibs_cbs_cst coverage 1.0000, 0 invalid. Withheld originally only because that catalog's declared specificity 0.75 caps the objective score below the 0.90 gate.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -10437,7 +9377,6 @@
       <c r="G178" t="n">
         <v>0.0983</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
         <v>0.9235</v>
       </c>
@@ -10467,11 +9406,6 @@
       <c r="O178" t="n">
         <v>0.85</v>
       </c>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
-      <c r="T178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -10520,18 +9454,22 @@
           <t>The candidate 'FI Nº do documento' has a high name confidence and matches the numeric format of the document number.</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
       <c r="P179" t="n">
         <v>0.8</v>
       </c>
       <c r="Q179" t="n">
         <v>0.85</v>
       </c>
-      <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
-      <c r="T179" t="inlineStr"/>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>CAVEAT: source is 61% blank by nature (c43 fills 7113/18209, 39.07%), so 11096 rows deliver an empty value - source sparsity, not a mapping fault. Column also mixes SAP document ranges (~36% carry a material rather than an FI document). Model spec is thin (20/209 populated). Confirm both ranges belong in this canonical field.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -10559,7 +9497,6 @@
       <c r="G180" t="n">
         <v>0.1645</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="n">
         <v>1</v>
       </c>
@@ -10578,14 +9515,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
-      <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
-      <c r="T180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -10596,8 +9525,6 @@
           <t>Exportador</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="n">
         <v>0.7949000000000001</v>
       </c>
@@ -10628,18 +9555,12 @@
           <t>The 'Exportador' column is empty with no valid data to support a mapping.</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
       <c r="P181" t="n">
         <v>0</v>
       </c>
       <c r="Q181" t="n">
         <v>0</v>
       </c>
-      <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr"/>
-      <c r="T181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -10650,8 +9571,6 @@
           <t>Lote</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
         <v>0.7887</v>
       </c>
@@ -10682,18 +9601,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
       <c r="P182" t="n">
         <v>0.7887</v>
       </c>
       <c r="Q182" t="n">
         <v>0.7887</v>
       </c>
-      <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
-      <c r="T182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -10704,8 +9617,6 @@
           <t>Tp.declar.importação</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
         <v>0.8067</v>
       </c>
@@ -10736,18 +9647,12 @@
           <t>All candidates have insufficient evidence and do not match the expected semantic role.</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
       <c r="P183" t="n">
         <v>0</v>
       </c>
       <c r="Q183" t="n">
         <v>0</v>
       </c>
-      <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr"/>
-      <c r="T183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -10758,8 +9663,6 @@
           <t>Código Fornecedor Início</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="n">
         <v>0.7741</v>
       </c>
@@ -10790,18 +9693,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
       <c r="P184" t="n">
         <v>0.9</v>
       </c>
       <c r="Q184" t="n">
         <v>0.85</v>
       </c>
-      <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
-      <c r="T184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -10829,7 +9726,6 @@
       <c r="G185" t="n">
         <v>0.1822</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="n">
         <v>0.98</v>
       </c>
@@ -10848,14 +9744,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
-      <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
-      <c r="T185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -10866,8 +9754,6 @@
           <t>Data do desembaraço aduaneiro</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="n">
         <v>0.8212</v>
       </c>
@@ -10898,18 +9784,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
       <c r="P186" t="n">
         <v>0.8212</v>
       </c>
       <c r="Q186" t="n">
         <v>0.8212</v>
       </c>
-      <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
-      <c r="T186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -10958,18 +9838,12 @@
           <t>The candidate 'NF Data documento' has a high name confidence and matches the datetime type expected for 'Data de registro documento de importação', despite the original column being empty.</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
       <c r="P187" t="n">
         <v>0</v>
       </c>
       <c r="Q187" t="n">
         <v>0.8294</v>
       </c>
-      <c r="R187" t="inlineStr"/>
-      <c r="S187" t="inlineStr"/>
-      <c r="T187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -11018,18 +9892,12 @@
           <t>The candidate 'FI Data document' has a strong name match and valid datetime format, aligning with the expected document date.</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
       <c r="P188" t="n">
         <v>0.8176</v>
       </c>
       <c r="Q188" t="n">
         <v>0.8176</v>
       </c>
-      <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr"/>
-      <c r="T188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -11078,18 +9946,12 @@
           <t>The header 'Item do pedido' closely matches the canonical 'Item' with high name confidence, despite a high zero fraction.</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
       <c r="P189" t="n">
         <v>0.5</v>
       </c>
       <c r="Q189" t="n">
         <v>0.908</v>
       </c>
-      <c r="R189" t="inlineStr"/>
-      <c r="S189" t="inlineStr"/>
-      <c r="T189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -11100,8 +9962,6 @@
           <t>Elemento PEP</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="n">
         <v>0.7837</v>
       </c>
@@ -11132,18 +9992,12 @@
           <t>All candidate columns contain numeric values but do not semantically align with the empty 'Elemento PEP' header.</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
       <c r="P190" t="n">
         <v>0</v>
       </c>
       <c r="Q190" t="n">
         <v>0</v>
       </c>
-      <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
-      <c r="T190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -11171,7 +10025,6 @@
       <c r="G191" t="n">
         <v>0.08749999999999999</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="n">
         <v>0.98</v>
       </c>
@@ -11190,14 +10043,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
-      <c r="T191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -11208,8 +10053,6 @@
           <t>Tipo Frete</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
         <v>0.8394</v>
       </c>
@@ -11240,18 +10083,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
       <c r="P192" t="n">
         <v>0.5</v>
       </c>
       <c r="Q192" t="n">
         <v>0.8394</v>
       </c>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
-      <c r="T192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -11279,7 +10116,6 @@
       <c r="G193" t="n">
         <v>0.1811</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="n">
         <v>0.98</v>
       </c>
@@ -11298,14 +10134,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
-      <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
-      <c r="T193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -11316,8 +10144,6 @@
           <t>Tipo de Imposto IPI</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
       <c r="E194" t="n">
         <v>0.8506</v>
       </c>
@@ -11348,18 +10174,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
       <c r="P194" t="n">
         <v>0.7375</v>
       </c>
       <c r="Q194" t="n">
         <v>0.8506</v>
       </c>
-      <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
-      <c r="T194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -11370,8 +10190,6 @@
           <t>Nº item do documento</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" t="n">
         <v>0.861</v>
       </c>
@@ -11402,18 +10220,12 @@
           <t>All candidates exhibit semantic-role conflicts with the item ID, indicating they do not match the expected document ID role.</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
       <c r="P195" t="n">
         <v>0</v>
       </c>
       <c r="Q195" t="n">
         <v>0</v>
       </c>
-      <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
-      <c r="T195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -11462,18 +10274,12 @@
           <t>The column 'NF Parceiro descrição' has a high name confidence and a strong semantic match with the 'Descrição' column, despite some differences in sample values.</t>
         </is>
       </c>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
       <c r="P196" t="n">
         <v>0.8</v>
       </c>
       <c r="Q196" t="n">
         <v>0.85</v>
       </c>
-      <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
-      <c r="T196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -11501,7 +10307,6 @@
       <c r="G197" t="n">
         <v>0.2081</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="n">
         <v>1</v>
       </c>
@@ -11520,14 +10325,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
-      <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
-      <c r="T197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -11555,7 +10352,6 @@
       <c r="G198" t="n">
         <v>0.0789</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
         <v>1</v>
       </c>
@@ -11574,14 +10370,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
-      <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr"/>
-      <c r="T198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -11609,7 +10397,6 @@
       <c r="G199" t="n">
         <v>0.1301</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
         <v>0.9468</v>
       </c>
@@ -11628,14 +10415,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
-      <c r="R199" t="inlineStr"/>
-      <c r="S199" t="inlineStr"/>
-      <c r="T199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -11663,7 +10442,6 @@
       <c r="G200" t="n">
         <v>0.2096</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
         <v>1</v>
       </c>
@@ -11682,14 +10460,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
-      <c r="R200" t="inlineStr"/>
-      <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -11700,8 +10470,6 @@
           <t>Município do Local de Fim</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="n">
         <v>0.7055</v>
       </c>
@@ -11732,18 +10500,12 @@
           <t>No viable candidate exists due to lack of non-empty values in the target column.</t>
         </is>
       </c>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
       <c r="P201" t="n">
         <v>0</v>
       </c>
       <c r="Q201" t="n">
         <v>0</v>
       </c>
-      <c r="R201" t="inlineStr"/>
-      <c r="S201" t="inlineStr"/>
-      <c r="T201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -11754,8 +10516,6 @@
           <t>Município do Local de Início</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="n">
         <v>0.7319</v>
       </c>
@@ -11786,18 +10546,12 @@
           <t>No suitable candidate matches the semantic role of 'Município do Local de Início'.</t>
         </is>
       </c>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
       <c r="P202" t="n">
         <v>0</v>
       </c>
       <c r="Q202" t="n">
         <v>0</v>
       </c>
-      <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr"/>
-      <c r="T202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -11808,8 +10562,6 @@
           <t>IVA</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="n">
         <v>0.8467</v>
       </c>
@@ -11840,18 +10592,12 @@
           <t>All candidates have semantic header conflicts with IVA, indicating they do not represent the same business meaning.</t>
         </is>
       </c>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
       <c r="P203" t="n">
         <v>0</v>
       </c>
       <c r="Q203" t="n">
         <v>0</v>
       </c>
-      <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
-      <c r="T203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -11862,8 +10608,6 @@
           <t>Nome Transportadora</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="n">
         <v>0.7794</v>
       </c>
@@ -11894,18 +10638,12 @@
           <t>The candidate columns contain no relevant data to map to 'Nome Transportadora'.</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
       <c r="P204" t="n">
         <v>0</v>
       </c>
       <c r="Q204" t="n">
         <v>0</v>
       </c>
-      <c r="R204" t="inlineStr"/>
-      <c r="S204" t="inlineStr"/>
-      <c r="T204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -11933,7 +10671,6 @@
       <c r="G205" t="n">
         <v>0.0613</v>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
         <v>0.9404</v>
       </c>
@@ -11963,11 +10700,6 @@
       <c r="O205" t="n">
         <v>0.9049</v>
       </c>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
-      <c r="R205" t="inlineStr"/>
-      <c r="S205" t="inlineStr"/>
-      <c r="T205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -12016,18 +10748,12 @@
           <t>The candidate 'FI Nº do documento' has a high name confidence and a substantial number of non-empty values, indicating it likely represents the same semantic role as 'Nº doc.importação'.</t>
         </is>
       </c>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
       <c r="P206" t="n">
         <v>0.8</v>
       </c>
       <c r="Q206" t="n">
         <v>0.8624000000000001</v>
       </c>
-      <c r="R206" t="inlineStr"/>
-      <c r="S206" t="inlineStr"/>
-      <c r="T206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -12038,8 +10764,6 @@
           <t>Preço líq.</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr"/>
-      <c r="D207" t="inlineStr"/>
       <c r="E207" t="n">
         <v>0.8081</v>
       </c>
@@ -12070,18 +10794,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
       <c r="P207" t="n">
         <v>0.8081</v>
       </c>
       <c r="Q207" t="n">
         <v>0.8081</v>
       </c>
-      <c r="R207" t="inlineStr"/>
-      <c r="S207" t="inlineStr"/>
-      <c r="T207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -12130,18 +10848,12 @@
           <t>The candidate 'Valor líquido do ped' has a high name confidence but a significant zero fraction and low median values, indicating it may not represent the same business meaning as 'Valor líquido'.</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
       <c r="P208" t="n">
         <v>0</v>
       </c>
       <c r="Q208" t="n">
         <v>0.8778</v>
       </c>
-      <c r="R208" t="inlineStr"/>
-      <c r="S208" t="inlineStr"/>
-      <c r="T208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -12190,18 +10902,12 @@
           <t>The candidate 'Nº NF-e' has a high name confidence and matches the expected format for an invoice number, despite the numeric nature of its values.</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
       <c r="P209" t="n">
         <v>0</v>
       </c>
       <c r="Q209" t="n">
         <v>0.8912</v>
       </c>
-      <c r="R209" t="inlineStr"/>
-      <c r="S209" t="inlineStr"/>
-      <c r="T209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -12250,18 +10956,22 @@
           <t>The candidate 'Nº NF-e' has a high name confidence and a substantial non-empty count, indicating it likely represents the 'Número de nota fiscal eletrônica'.</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
       <c r="P210" t="n">
         <v>0.9</v>
       </c>
       <c r="Q210" t="n">
         <v>0.9009</v>
       </c>
-      <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr"/>
-      <c r="T210" t="inlineStr"/>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>NF-e number routed here, NOT to m32, per the firm's own de_para_procosa.xlsx (sheet SAP), whose m32 header cell reads verbatim: 'No da Nota Fiscal - coloquei o numero da Nota Fiscal Eletronica na coluna GZ'. GZ = sheet col 208 = m209, which that file fills 98/99 while leaving m32 blank 0/99. CAVEAT: 20 of 18209 source rows blank; 637 (3.5%) are 4-7 chars rather than zero-padded to 9. Procosa-specific routing.</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -12310,18 +11020,12 @@
           <t>The column 'Total' has a high name confidence and matches the expected numeric type for 'Valor Total do Item', despite a broader numeric range.</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
       <c r="P211" t="n">
         <v>0.89</v>
       </c>
       <c r="Q211" t="n">
         <v>0.89</v>
       </c>
-      <c r="R211" t="inlineStr"/>
-      <c r="S211" t="inlineStr"/>
-      <c r="T211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -12332,8 +11036,6 @@
           <t>Nome do Fornecedor do Local de Início</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
       <c r="E212" t="n">
         <v>0.7405</v>
       </c>
@@ -12364,18 +11066,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
       <c r="P212" t="n">
         <v>0.4104</v>
       </c>
       <c r="Q212" t="n">
         <v>0.7405</v>
       </c>
-      <c r="R212" t="inlineStr"/>
-      <c r="S212" t="inlineStr"/>
-      <c r="T212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -12386,8 +11082,6 @@
           <t>Cód Transportadora</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" t="n">
         <v>0.7848000000000001</v>
       </c>
@@ -12418,18 +11112,12 @@
           <t>No viable candidates match the semantic role of 'Cód Transportadora' as all candidates are unrelated.</t>
         </is>
       </c>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
       <c r="P213" t="n">
         <v>0</v>
       </c>
       <c r="Q213" t="n">
         <v>0</v>
       </c>
-      <c r="R213" t="inlineStr"/>
-      <c r="S213" t="inlineStr"/>
-      <c r="T213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12457,7 +11145,6 @@
       <c r="G214" t="n">
         <v>0.2041</v>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="n">
         <v>0.98</v>
       </c>
@@ -12476,14 +11163,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
-      <c r="R214" t="inlineStr"/>
-      <c r="S214" t="inlineStr"/>
-      <c r="T214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12511,7 +11190,6 @@
       <c r="G215" t="n">
         <v>0.052</v>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="n">
         <v>1</v>
       </c>
@@ -12530,14 +11208,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
-      <c r="R215" t="inlineStr"/>
-      <c r="S215" t="inlineStr"/>
-      <c r="T215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -12586,18 +11256,12 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
       <c r="P216" t="n">
         <v>0</v>
       </c>
       <c r="Q216" t="n">
         <v>0</v>
       </c>
-      <c r="R216" t="inlineStr"/>
-      <c r="S216" t="inlineStr"/>
-      <c r="T216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -12646,18 +11310,12 @@
           <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
         </is>
       </c>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
       <c r="P217" t="n">
         <v>0</v>
       </c>
       <c r="Q217" t="n">
         <v>0</v>
       </c>
-      <c r="R217" t="inlineStr"/>
-      <c r="S217" t="inlineStr"/>
-      <c r="T217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -12706,18 +11364,12 @@
           <t>Distinctive non-zero sample values overlap exactly with this candidate and not with the competing columns.</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
       <c r="P218" t="n">
         <v>0.8486</v>
       </c>
       <c r="Q218" t="n">
         <v>0.8486</v>
       </c>
-      <c r="R218" t="inlineStr"/>
-      <c r="S218" t="inlineStr"/>
-      <c r="T218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -12766,18 +11418,12 @@
           <t>The column 'Direito' has a strong name match and significant distinctive sample overlap with 'Lei tributária PIS', despite some semantic conflicts.</t>
         </is>
       </c>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
       <c r="P219" t="n">
         <v>0.6667</v>
       </c>
       <c r="Q219" t="n">
         <v>0.8073</v>
       </c>
-      <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr"/>
-      <c r="T219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -12788,8 +11434,6 @@
           <t>CST IPI</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr"/>
-      <c r="D220" t="inlineStr"/>
       <c r="E220" t="n">
         <v>0.7872</v>
       </c>
@@ -12820,18 +11464,12 @@
           <t>The candidate 'CBS IBS Taxsituation' conflicts with the expected tax family for CST IPI.</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
       <c r="P220" t="n">
         <v>0</v>
       </c>
       <c r="Q220" t="n">
         <v>0</v>
       </c>
-      <c r="R220" t="inlineStr"/>
-      <c r="S220" t="inlineStr"/>
-      <c r="T220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -12842,8 +11480,6 @@
           <t>CST COFINS</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr"/>
-      <c r="D221" t="inlineStr"/>
       <c r="E221" t="n">
         <v>0.8132</v>
       </c>
@@ -12874,18 +11510,12 @@
           <t>All candidates exhibit semantic header conflicts or lack relevant data evidence to support a mapping.</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
       <c r="P221" t="n">
         <v>0</v>
       </c>
       <c r="Q221" t="n">
         <v>0</v>
       </c>
-      <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr"/>
-      <c r="T221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -12896,8 +11526,6 @@
           <t>CST PIS</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr"/>
-      <c r="D222" t="inlineStr"/>
       <c r="E222" t="n">
         <v>0.8483000000000001</v>
       </c>
@@ -12928,18 +11556,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
       <c r="P222" t="n">
         <v>0</v>
       </c>
       <c r="Q222" t="n">
         <v>0.8483000000000001</v>
       </c>
-      <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr"/>
-      <c r="T222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -12950,8 +11572,6 @@
           <t>CST ICMS</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr"/>
-      <c r="D223" t="inlineStr"/>
       <c r="E223" t="n">
         <v>0.819</v>
       </c>
@@ -12982,18 +11602,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr"/>
       <c r="P223" t="n">
         <v>0.75</v>
       </c>
       <c r="Q223" t="n">
         <v>0.75</v>
       </c>
-      <c r="R223" t="inlineStr"/>
-      <c r="S223" t="inlineStr"/>
-      <c r="T223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -13004,8 +11618,6 @@
           <t>Região do local do desembaraço aduaneiro</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr"/>
-      <c r="D224" t="inlineStr"/>
       <c r="E224" t="n">
         <v>0.7481</v>
       </c>
@@ -13036,18 +11648,12 @@
           <t>All candidate columns contain no relevant data to support a mapping.</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
       <c r="P224" t="n">
         <v>0</v>
       </c>
       <c r="Q224" t="n">
         <v>0</v>
       </c>
-      <c r="R224" t="inlineStr"/>
-      <c r="S224" t="inlineStr"/>
-      <c r="T224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -13058,8 +11664,6 @@
           <t>UF do Local de Fim</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" t="n">
         <v>0.7638</v>
       </c>
@@ -13090,18 +11694,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
       <c r="P225" t="n">
         <v>0.7638</v>
       </c>
       <c r="Q225" t="n">
         <v>0.7638</v>
       </c>
-      <c r="R225" t="inlineStr"/>
-      <c r="S225" t="inlineStr"/>
-      <c r="T225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -13112,8 +11710,6 @@
           <t>UF do Local de Início</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="n">
         <v>0.7534</v>
       </c>
@@ -13144,18 +11740,12 @@
           <t>No candidate column matches the semantic role of 'UF do Local de Início'.</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
       <c r="P226" t="n">
         <v>0</v>
       </c>
       <c r="Q226" t="n">
         <v>0</v>
       </c>
-      <c r="R226" t="inlineStr"/>
-      <c r="S226" t="inlineStr"/>
-      <c r="T226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -13183,7 +11773,6 @@
       <c r="G227" t="n">
         <v>0.2285</v>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="n">
         <v>1</v>
       </c>
@@ -13202,14 +11791,6 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
-      <c r="R227" t="inlineStr"/>
-      <c r="S227" t="inlineStr"/>
-      <c r="T227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -13220,8 +11801,6 @@
           <t>Local do desembaraço aduaneiro</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr"/>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" t="n">
         <v>0.7538</v>
       </c>
@@ -13252,18 +11831,12 @@
           <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
       <c r="P228" t="n">
         <v>0.7538</v>
       </c>
       <c r="Q228" t="n">
         <v>0.7538</v>
       </c>
-      <c r="R228" t="inlineStr"/>
-      <c r="S228" t="inlineStr"/>
-      <c r="T228" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mapping_sap_procosa_full.xlsx
+++ b/mapping_sap_procosa_full.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T228"/>
+  <dimension ref="A1:W228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,17 +515,32 @@
           <t>llm_final_confidence</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>decided_by</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>supported_by</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>vetoed_by</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>reviewer_status</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>correct_client_column</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>reviewer_note</t>
         </is>
@@ -586,10 +601,21 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>no_mapping_exists</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>c96 is the 3-digit CST ('000'/'410'), claimed by m176 - a situation code, not a tax type. No column in this export holds a 4-char SAP tax type (full scan: 1 hit, c11 'PR05', already accepted to m29). Model m1 is 0/209.</t>
         </is>
@@ -639,6 +665,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -693,6 +730,17 @@
       <c r="Q4" t="n">
         <v>0.98</v>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>unrecorded</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>resolver + semantic + unrecorded</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -738,6 +786,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -783,6 +842,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -828,6 +898,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -930,10 +1011,21 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>no_mapping_exists</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>c117 is a SAP X/blank boolean ('X' in 15296 rows, 1 distinct). Writing 'X' beside ICM3/IPI3/ICON/IPSN would fabricate a tax type.</t>
         </is>
@@ -983,6 +1075,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1028,6 +1131,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1073,6 +1187,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1129,10 +1254,21 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>CAVEAT: delivers an all-zero column (18209 filled, 1 distinct, 0 non-zero). Same precedent as m19. Originally withheld by 0.0014 of confidence.</t>
         </is>
@@ -1182,6 +1318,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1284,10 +1431,21 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>no_mapping_exists</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>c95 is a 3-char SAP tax-LAW code {RJ3:10929, RA0:5915, RH5:25} and a perfect 1:1 recode of the already-accepted c97, carrying zero independent information. The model has no 'Lei CBS/IBS' column.</t>
         </is>
@@ -1337,6 +1495,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1391,6 +1560,17 @@
       <c r="Q18" t="n">
         <v>0.98</v>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>resolver + semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1436,6 +1616,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1492,10 +1683,21 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>CAVEAT: delivers an all-zero column (18209 filled, 1 distinct, 0 non-zero). Legitimate fiscal data - precedent set by the already-accepted all-zero c101-&gt;m5 Isentas CBS. Populated, never empty.</t>
         </is>
@@ -1556,10 +1758,21 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Confirmed: third member of a set already accepted twice (c102-&gt;m6, c116-&gt;m13). Profiles near-identical: non-zero 9344/9400/9425, distinct 3285/3337/3355. Accepting two and withholding the third was arbitrary.</t>
         </is>
@@ -1666,10 +1879,21 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
           <t>no_mapping_exists</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>c110 is a SAP X/blank boolean, 1 distinct. No Imposto Seletivo block exists: regex seletiv|excise|imp.sel over all 118 headers returns ZERO hits, and c98-c118 is a strict 3x7 grid (CBS/IBSS/IBSM) with no fourth block.</t>
         </is>
@@ -1730,10 +1954,21 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
           <t>no_mapping_exists</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>c61 is Base FCP (Fundo de Combate a Pobreza), an ICMS surcharge - a different tax. 1 distinct, 0 non-zero. Correct home is m112. Procosa levies no IS.</t>
         </is>
@@ -1794,10 +2029,21 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
           <t>no_mapping_exists</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>c62 is Aliquota FCP, same group; 1 distinct, 0 non-zero. Correct home is m113. Procosa levies no IS.</t>
         </is>
@@ -1858,10 +2104,21 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
           <t>no_mapping_exists</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>c77 'Valor do imposto' is a generic unqualified label, 1 distinct, 0 non-zero. Shipping it would assert an Imposto Seletivo of exactly zero on 18209 invoices - a positive claim the data does not support.</t>
         </is>
@@ -1922,10 +2179,21 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
           <t>no_mapping_exists</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>c115 is the IBSM period's exempt-base slot and belongs to m12. Procosa levies no IS.</t>
         </is>
@@ -1986,10 +2254,21 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
           <t>no_mapping_exists</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>c60 is real ICMS money (7953 non-zero rows, R$66,303,765.04) and belongs to m45 by the book identity. Would misattribute R$66.3M of ICMS to a tax the client does not levy.</t>
         </is>
@@ -2085,6 +2364,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2141,10 +2431,21 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>Confirmed: c4 is 12 distinct over a 14-day window, the posting-period signature. Swap with c3 refuted quantitatively.</t>
         </is>
@@ -2205,10 +2506,21 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>Confirmed: chave decomposition proves m31 is not the NF number (m32==key[25:34] in 209/209 model rows, m31 in 0/209). c1 is 18209/18209 filled, 2823 distinct, 100% 7-digit, matching model m31 shape.</t>
         </is>
@@ -2267,6 +2579,17 @@
       <c r="Q33" t="n">
         <v>0.93</v>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2312,6 +2635,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2368,6 +2702,17 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>semantic + catalog</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2422,6 +2767,17 @@
       <c r="Q36" t="n">
         <v>0.8588</v>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2478,10 +2834,21 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>CAVEAT: 604 of 18209 rows (3.32%) hold 6-digit IDs and ~3090 hold alphanumeric partner codes ('BAP283G','COS826'), against model m36's 7-digit numeric exemplars. Swap with c6 arithmetically impossible (c5 83% pure-numeric; c6 0% numeric).</t>
         </is>
@@ -2532,15 +2899,15 @@
       <c r="Q38" t="n">
         <v>0</v>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>incorrect</t>
         </is>
       </c>
-      <c r="S38" t="n">
+      <c r="V38" t="n">
         <v>6</v>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>Confirmed: only party-name column in the export, 18209/18209 filled, 258 distinct, matching c5's 267 partner IDs; shares the SAP NAME1 35-char truncation with model m37.</t>
         </is>
@@ -2591,15 +2958,15 @@
       <c r="Q39" t="n">
         <v>0</v>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>incorrect</t>
         </is>
       </c>
-      <c r="S39" t="n">
+      <c r="V39" t="n">
         <v>32</v>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>Only tax-ID column in the export and only fiscal-ID column in the model. 18154/18192 (99.79%) pass the CNPJ check digit. *** CAVEAT: MUST NOT SHIP UNNORMALISED. All values are punctuated ('71.960.736/0001-50'); model m38 is 209/209 bare digits. apply_invoice_mapping.py copies verbatim with no normalisation hook. Strip non-digits before delivery or any join. 38 rows never resolve (foreign/placeholder); 17 blank. ***</t>
         </is>
@@ -2704,6 +3071,17 @@
       <c r="Q41" t="n">
         <v>0.85</v>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2758,6 +3136,17 @@
       <c r="Q42" t="n">
         <v>0.9063</v>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>resolver + semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2803,6 +3192,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2905,10 +3305,21 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>Confirmed: book identity c8 Total == c12 + c59 + c60 holds on 17022/18209 (93.5%) vs 51.3% / 50.5% / 8.4% for the alternatives. Direction fixed by accepted precedents c68-&gt;m51, c70-&gt;m124, c101-&gt;m5. NOTE: carries R$46.4M (54.3%) of base-reduction excess rather than true exemption.</t>
         </is>
@@ -2969,10 +3380,21 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>Confirmed: the firm's own de_para for this client has Outras ICMS ~= Outras IPI (equal rowwise 96/99). Only this pairing reproduces it: c60==c68 on 12263/18209 with 7881 both non-zero; the swapped pairing has 6. NOTE: also explains the 319 delivered rows with ICMS value&gt;0 against a zero base.</t>
         </is>
@@ -3031,6 +3453,17 @@
       <c r="Q47" t="n">
         <v>0</v>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3131,6 +3564,17 @@
       <c r="Q49" t="n">
         <v>0.9142</v>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>resolver + semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3176,6 +3620,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3232,10 +3687,21 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>CAVEAT: near-vacuous - 18209 filled but only 6 NON-ZERO rows (7 distinct), R$199,626.89 across 6 export lines. Not empty, so not a fabrication, but of very low value. Shipped for family completeness with ICMS/IPI/CBS/IBS/IBSM.</t>
         </is>
@@ -3285,6 +3751,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3339,6 +3816,17 @@
       <c r="Q53" t="n">
         <v>0.8959</v>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>resolver + semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3384,6 +3872,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3438,6 +3937,17 @@
       <c r="Q55" t="n">
         <v>0.9123</v>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>resolver + semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3483,6 +3993,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3620,6 +4141,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3711,6 +4243,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3767,10 +4310,21 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>Confirmed: model invariant m61&lt;=m30 holds 209/209; client reproduces it exactly, c3&lt;=c4 in 18209/18209. Swap would fail in 9702 rows (53.28%).</t>
         </is>
@@ -3967,6 +4521,17 @@
       <c r="Q66" t="n">
         <v>0.8283</v>
       </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4021,6 +4586,17 @@
       <c r="Q67" t="n">
         <v>0.85</v>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4075,6 +4651,17 @@
       <c r="Q68" t="n">
         <v>0.8231000000000001</v>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4129,6 +4716,17 @@
       <c r="Q69" t="n">
         <v>0.8423</v>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4367,6 +4965,17 @@
       <c r="Q74" t="n">
         <v>0.9</v>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4605,6 +5214,17 @@
       <c r="Q79" t="n">
         <v>0.8714</v>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4659,6 +5279,17 @@
       <c r="Q80" t="n">
         <v>0.8935</v>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4759,6 +5390,17 @@
       <c r="Q82" t="n">
         <v>0.8925</v>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4850,6 +5492,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4895,6 +5548,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5685,6 +6349,17 @@
       <c r="Q102" t="n">
         <v>0</v>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5969,6 +6644,17 @@
       <c r="Q108" t="n">
         <v>0.827</v>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6069,6 +6755,21 @@
       <c r="Q110" t="n">
         <v>0.834</v>
       </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>family_conflict</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6123,6 +6824,21 @@
       <c r="Q111" t="n">
         <v>0.8368</v>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>family_conflict</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6177,6 +6893,21 @@
       <c r="Q112" t="n">
         <v>0</v>
       </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>family_conflict</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6231,6 +6962,17 @@
       <c r="Q113" t="n">
         <v>0.8895999999999999</v>
       </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6285,6 +7027,17 @@
       <c r="Q114" t="n">
         <v>0.9056</v>
       </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -6339,6 +7092,17 @@
       <c r="Q115" t="n">
         <v>0.9292</v>
       </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6393,6 +7157,17 @@
       <c r="Q116" t="n">
         <v>0.8229</v>
       </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -6447,6 +7222,17 @@
       <c r="Q117" t="n">
         <v>0</v>
       </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6639,6 +7425,17 @@
       <c r="Q121" t="n">
         <v>0</v>
       </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -6695,10 +7492,21 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T122" t="inlineStr">
+      <c r="W122" t="inlineStr">
         <is>
           <t>Confirmed: exact structural twin of the already-accepted c70-&gt;m124 Outras PIS (5266 vs 5265 distinct, 12277 vs 12276 non-zero).</t>
         </is>
@@ -6803,6 +7611,17 @@
       <c r="Q124" t="n">
         <v>0.8593</v>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -6848,6 +7667,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7132,6 +7962,17 @@
       <c r="Q131" t="n">
         <v>0.8705000000000001</v>
       </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7970,10 +8811,21 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T149" t="inlineStr">
+      <c r="W149" t="inlineStr">
         <is>
           <t>Confirmed: residual of the proven date trio; c4&lt;=c26 in 18179/18209 (99.84%), mirroring model m30==m148 in 208/209.</t>
         </is>
@@ -8446,6 +9298,17 @@
       <c r="Q159" t="n">
         <v>0.9367</v>
       </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -8592,6 +9455,17 @@
       <c r="Q162" t="n">
         <v>0.8894</v>
       </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8784,6 +9658,17 @@
       <c r="Q166" t="n">
         <v>0.8828</v>
       </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -8838,6 +9723,17 @@
       <c r="Q167" t="n">
         <v>0.8863</v>
       </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -8984,6 +9880,17 @@
       <c r="Q170" t="n">
         <v>0.8962</v>
       </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -9038,6 +9945,17 @@
       <c r="Q171" t="n">
         <v>0.9145</v>
       </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -9092,6 +10010,17 @@
       <c r="Q172" t="n">
         <v>0.9141</v>
       </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9229,6 +10158,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -9342,10 +10282,21 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>resolver + semantic + catalog</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T177" t="inlineStr">
+      <c r="W177" t="inlineStr">
         <is>
           <t>Confirmed structurally: c96==c97[:3] in 16869/16869 rows (100%), and c97-&gt;m177 is already accepted. Catalog ibs_cbs_cst coverage 1.0000, 0 invalid. Withheld originally only because that catalog's declared specificity 0.75 caps the objective score below the 0.90 gate.</t>
         </is>
@@ -9406,6 +10357,17 @@
       <c r="O178" t="n">
         <v>0.85</v>
       </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>semantic + catalog (agrees)</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -9462,10 +10424,21 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T179" t="inlineStr">
+      <c r="W179" t="inlineStr">
         <is>
           <t>CAVEAT: source is 61% blank by nature (c43 fills 7113/18209, 39.07%), so 11096 rows deliver an empty value - source sparsity, not a mapping fault. Column also mixes SAP document ranges (~36% carry a material rather than an FI document). Model spec is thin (20/209 populated). Confirm both ranges belong in this canonical field.</t>
         </is>
@@ -9515,6 +10488,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -9744,6 +10728,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -9844,6 +10839,17 @@
       <c r="Q187" t="n">
         <v>0.8294</v>
       </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -9898,6 +10904,17 @@
       <c r="Q188" t="n">
         <v>0.8176</v>
       </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -9952,6 +10969,17 @@
       <c r="Q189" t="n">
         <v>0.908</v>
       </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -10043,6 +11071,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -10134,6 +11173,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -10280,6 +11330,17 @@
       <c r="Q196" t="n">
         <v>0.85</v>
       </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -10325,6 +11386,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -10370,6 +11442,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -10415,6 +11498,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -10460,6 +11554,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -10700,6 +11805,17 @@
       <c r="O205" t="n">
         <v>0.9049</v>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>catalog</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>semantic + catalog</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -10754,6 +11870,17 @@
       <c r="Q206" t="n">
         <v>0.8624000000000001</v>
       </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -10854,6 +11981,17 @@
       <c r="Q208" t="n">
         <v>0.8778</v>
       </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -10908,6 +12046,17 @@
       <c r="Q209" t="n">
         <v>0.8912</v>
       </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -10964,10 +12113,21 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr">
+        <is>
           <t>correct</t>
         </is>
       </c>
-      <c r="T210" t="inlineStr">
+      <c r="W210" t="inlineStr">
         <is>
           <t>NF-e number routed here, NOT to m32, per the firm's own de_para_procosa.xlsx (sheet SAP), whose m32 header cell reads verbatim: 'No da Nota Fiscal - coloquei o numero da Nota Fiscal Eletronica na coluna GZ'. GZ = sheet col 208 = m209, which that file fills 98/99 while leaving m32 blank 0/99. CAVEAT: 20 of 18209 source rows blank; 637 (3.5%) are 4-7 chars rather than zero-padded to 9. Procosa-specific routing.</t>
         </is>
@@ -11026,6 +12186,17 @@
       <c r="Q211" t="n">
         <v>0.89</v>
       </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>resolver + semantic</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -11163,6 +12334,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>arithmetic</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>semantic + arithmetic</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -11208,6 +12390,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -11262,6 +12455,17 @@
       <c r="Q216" t="n">
         <v>0</v>
       </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -11316,6 +12520,17 @@
       <c r="Q217" t="n">
         <v>0</v>
       </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -11370,6 +12585,17 @@
       <c r="Q218" t="n">
         <v>0.8486</v>
       </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>unrecorded</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>resolver + semantic + unrecorded</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -11424,6 +12650,17 @@
       <c r="Q219" t="n">
         <v>0.8073</v>
       </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>unrecorded</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>resolver + semantic + unrecorded</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -11791,6 +13028,17 @@
           <t>Accepted from header similarity with a clear lead over the runner-up.</t>
         </is>
       </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
